--- a/artfynd/A 41884-2025 artfynd.xlsx
+++ b/artfynd/A 41884-2025 artfynd.xlsx
@@ -879,45 +879,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128297215</v>
+        <v>128300242</v>
       </c>
       <c r="B4" t="n">
-        <v>80132</v>
+        <v>98504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632389</v>
+        <v>632064</v>
       </c>
       <c r="R4" t="n">
-        <v>6898813</v>
+        <v>6898932</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -947,19 +956,9 @@
           <t>2025-09-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,54 +985,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128300242</v>
+        <v>128297215</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>80132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632064</v>
+        <v>632389</v>
       </c>
       <c r="R5" t="n">
-        <v>6898932</v>
+        <v>6898813</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,9 +1053,19 @@
           <t>2025-09-08</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 41884-2025 artfynd.xlsx
+++ b/artfynd/A 41884-2025 artfynd.xlsx
@@ -879,54 +879,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128300242</v>
+        <v>128297215</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>80132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632064</v>
+        <v>632389</v>
       </c>
       <c r="R4" t="n">
-        <v>6898932</v>
+        <v>6898813</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -956,9 +947,19 @@
           <t>2025-09-08</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,45 +986,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128297215</v>
+        <v>128300242</v>
       </c>
       <c r="B5" t="n">
-        <v>80132</v>
+        <v>98504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632389</v>
+        <v>632064</v>
       </c>
       <c r="R5" t="n">
-        <v>6898813</v>
+        <v>6898932</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1053,19 +1063,9 @@
           <t>2025-09-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 41884-2025 artfynd.xlsx
+++ b/artfynd/A 41884-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128297500</v>
+        <v>128299233</v>
       </c>
       <c r="B2" t="n">
-        <v>92287</v>
+        <v>95830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632308</v>
+        <v>632004</v>
       </c>
       <c r="R2" t="n">
-        <v>6898776</v>
+        <v>6898915</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -743,9 +743,19 @@
           <t>2025-09-08</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128299233</v>
+        <v>128297500</v>
       </c>
       <c r="B3" t="n">
-        <v>95822</v>
+        <v>92295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632004</v>
+        <v>632308</v>
       </c>
       <c r="R3" t="n">
-        <v>6898915</v>
+        <v>6898776</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -840,19 +850,9 @@
           <t>2025-09-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +882,7 @@
         <v>128297215</v>
       </c>
       <c r="B4" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128300242</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>98512</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>128299710</v>
       </c>
       <c r="B6" t="n">
-        <v>95702</v>
+        <v>95710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>128297225</v>
       </c>
       <c r="B7" t="n">
-        <v>80168</v>
+        <v>80171</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>128299667</v>
       </c>
       <c r="B8" t="n">
-        <v>92287</v>
+        <v>92295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>128299487</v>
       </c>
       <c r="B9" t="n">
-        <v>92254</v>
+        <v>92262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>128297461</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>128298782</v>
       </c>
       <c r="B11" t="n">
-        <v>91759</v>
+        <v>91767</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41884-2025 artfynd.xlsx
+++ b/artfynd/A 41884-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128299233</v>
       </c>
       <c r="B2" t="n">
-        <v>95830</v>
+        <v>95923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128297500</v>
       </c>
       <c r="B3" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128297215</v>
       </c>
       <c r="B4" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128300242</v>
       </c>
       <c r="B5" t="n">
-        <v>98512</v>
+        <v>98605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>128299710</v>
       </c>
       <c r="B6" t="n">
-        <v>95710</v>
+        <v>95803</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>128297225</v>
       </c>
       <c r="B7" t="n">
-        <v>80171</v>
+        <v>80224</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>128299667</v>
       </c>
       <c r="B8" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>128299487</v>
       </c>
       <c r="B9" t="n">
-        <v>92262</v>
+        <v>92354</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>128297461</v>
       </c>
       <c r="B10" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>128298782</v>
       </c>
       <c r="B11" t="n">
-        <v>91767</v>
+        <v>91859</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41884-2025 artfynd.xlsx
+++ b/artfynd/A 41884-2025 artfynd.xlsx
@@ -879,45 +879,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128297215</v>
+        <v>128300242</v>
       </c>
       <c r="B4" t="n">
-        <v>80188</v>
+        <v>98605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632389</v>
+        <v>632064</v>
       </c>
       <c r="R4" t="n">
-        <v>6898813</v>
+        <v>6898932</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -947,19 +956,9 @@
           <t>2025-09-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,54 +985,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128300242</v>
+        <v>128297215</v>
       </c>
       <c r="B5" t="n">
-        <v>98605</v>
+        <v>80188</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632064</v>
+        <v>632389</v>
       </c>
       <c r="R5" t="n">
-        <v>6898932</v>
+        <v>6898813</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,9 +1053,19 @@
           <t>2025-09-08</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 41884-2025 artfynd.xlsx
+++ b/artfynd/A 41884-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128299233</v>
+        <v>128297500</v>
       </c>
       <c r="B2" t="n">
-        <v>95923</v>
+        <v>92387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632004</v>
+        <v>632308</v>
       </c>
       <c r="R2" t="n">
-        <v>6898915</v>
+        <v>6898776</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -743,19 +743,9 @@
           <t>2025-09-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128297500</v>
+        <v>128299233</v>
       </c>
       <c r="B3" t="n">
-        <v>92387</v>
+        <v>95923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632308</v>
+        <v>632004</v>
       </c>
       <c r="R3" t="n">
-        <v>6898776</v>
+        <v>6898915</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -850,9 +840,19 @@
           <t>2025-09-08</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,54 +879,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128300242</v>
+        <v>128297215</v>
       </c>
       <c r="B4" t="n">
-        <v>98605</v>
+        <v>80188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632064</v>
+        <v>632389</v>
       </c>
       <c r="R4" t="n">
-        <v>6898932</v>
+        <v>6898813</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -956,9 +947,19 @@
           <t>2025-09-08</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,45 +986,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128297215</v>
+        <v>128300242</v>
       </c>
       <c r="B5" t="n">
-        <v>80188</v>
+        <v>98605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632389</v>
+        <v>632064</v>
       </c>
       <c r="R5" t="n">
-        <v>6898813</v>
+        <v>6898932</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1053,19 +1063,9 @@
           <t>2025-09-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 41884-2025 artfynd.xlsx
+++ b/artfynd/A 41884-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128297500</v>
+        <v>128299233</v>
       </c>
       <c r="B2" t="n">
-        <v>92387</v>
+        <v>95935</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632308</v>
+        <v>632004</v>
       </c>
       <c r="R2" t="n">
-        <v>6898776</v>
+        <v>6898915</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -743,9 +743,19 @@
           <t>2025-09-08</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128299233</v>
+        <v>128297500</v>
       </c>
       <c r="B3" t="n">
-        <v>95923</v>
+        <v>92399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632004</v>
+        <v>632308</v>
       </c>
       <c r="R3" t="n">
-        <v>6898915</v>
+        <v>6898776</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -840,19 +850,9 @@
           <t>2025-09-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,45 +879,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128297215</v>
+        <v>128300242</v>
       </c>
       <c r="B4" t="n">
-        <v>80188</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632389</v>
+        <v>632064</v>
       </c>
       <c r="R4" t="n">
-        <v>6898813</v>
+        <v>6898932</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -947,19 +956,9 @@
           <t>2025-09-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,54 +985,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128300242</v>
+        <v>128297215</v>
       </c>
       <c r="B5" t="n">
-        <v>98605</v>
+        <v>80192</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632064</v>
+        <v>632389</v>
       </c>
       <c r="R5" t="n">
-        <v>6898932</v>
+        <v>6898813</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,9 +1053,19 @@
           <t>2025-09-08</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,7 +1095,7 @@
         <v>128299710</v>
       </c>
       <c r="B6" t="n">
-        <v>95803</v>
+        <v>95815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>128297225</v>
       </c>
       <c r="B7" t="n">
-        <v>80224</v>
+        <v>80228</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>128299667</v>
       </c>
       <c r="B8" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>128299487</v>
       </c>
       <c r="B9" t="n">
-        <v>92354</v>
+        <v>92366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>128297461</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>128298782</v>
       </c>
       <c r="B11" t="n">
-        <v>91859</v>
+        <v>91871</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41884-2025 artfynd.xlsx
+++ b/artfynd/A 41884-2025 artfynd.xlsx
@@ -879,54 +879,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128300242</v>
+        <v>128297215</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>80192</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632064</v>
+        <v>632389</v>
       </c>
       <c r="R4" t="n">
-        <v>6898932</v>
+        <v>6898813</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -956,9 +947,19 @@
           <t>2025-09-08</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,45 +986,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128297215</v>
+        <v>128300242</v>
       </c>
       <c r="B5" t="n">
-        <v>80192</v>
+        <v>98619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632389</v>
+        <v>632064</v>
       </c>
       <c r="R5" t="n">
-        <v>6898813</v>
+        <v>6898932</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1053,19 +1063,9 @@
           <t>2025-09-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 41884-2025 artfynd.xlsx
+++ b/artfynd/A 41884-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128299233</v>
       </c>
       <c r="B2" t="n">
-        <v>95935</v>
+        <v>95937</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128297500</v>
       </c>
       <c r="B3" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128297215</v>
       </c>
       <c r="B4" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128300242</v>
       </c>
       <c r="B5" t="n">
-        <v>98619</v>
+        <v>98622</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>128299710</v>
       </c>
       <c r="B6" t="n">
-        <v>95815</v>
+        <v>95817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>128297225</v>
       </c>
       <c r="B7" t="n">
-        <v>80228</v>
+        <v>80230</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>128299667</v>
       </c>
       <c r="B8" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>128299487</v>
       </c>
       <c r="B9" t="n">
-        <v>92366</v>
+        <v>92368</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>128297461</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>128298782</v>
       </c>
       <c r="B11" t="n">
-        <v>91871</v>
+        <v>91873</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41884-2025 artfynd.xlsx
+++ b/artfynd/A 41884-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128299233</v>
+        <v>128297500</v>
       </c>
       <c r="B2" t="n">
-        <v>95937</v>
+        <v>92401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632004</v>
+        <v>632308</v>
       </c>
       <c r="R2" t="n">
-        <v>6898915</v>
+        <v>6898776</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -743,19 +743,9 @@
           <t>2025-09-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128297500</v>
+        <v>128299233</v>
       </c>
       <c r="B3" t="n">
-        <v>92401</v>
+        <v>95937</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632308</v>
+        <v>632004</v>
       </c>
       <c r="R3" t="n">
-        <v>6898776</v>
+        <v>6898915</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -850,9 +840,19 @@
           <t>2025-09-08</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -989,7 +989,7 @@
         <v>128300242</v>
       </c>
       <c r="B5" t="n">
-        <v>98622</v>
+        <v>98625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 41884-2025 artfynd.xlsx
+++ b/artfynd/A 41884-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128297500</v>
+        <v>128299233</v>
       </c>
       <c r="B2" t="n">
-        <v>92401</v>
+        <v>95937</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632308</v>
+        <v>632004</v>
       </c>
       <c r="R2" t="n">
-        <v>6898776</v>
+        <v>6898915</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -743,9 +743,19 @@
           <t>2025-09-08</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128299233</v>
+        <v>128297500</v>
       </c>
       <c r="B3" t="n">
-        <v>95937</v>
+        <v>92401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632004</v>
+        <v>632308</v>
       </c>
       <c r="R3" t="n">
-        <v>6898915</v>
+        <v>6898776</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -840,19 +850,9 @@
           <t>2025-09-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:11</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 41884-2025 artfynd.xlsx
+++ b/artfynd/A 41884-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128299233</v>
       </c>
       <c r="B2" t="n">
-        <v>95937</v>
+        <v>95938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128297500</v>
       </c>
       <c r="B3" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128300242</v>
       </c>
       <c r="B5" t="n">
-        <v>98625</v>
+        <v>98626</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>128299710</v>
       </c>
       <c r="B6" t="n">
-        <v>95817</v>
+        <v>95818</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>128299667</v>
       </c>
       <c r="B8" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>128299487</v>
       </c>
       <c r="B9" t="n">
-        <v>92368</v>
+        <v>92369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>128298782</v>
       </c>
       <c r="B11" t="n">
-        <v>91873</v>
+        <v>91874</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41884-2025 artfynd.xlsx
+++ b/artfynd/A 41884-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128299233</v>
+        <v>128297500</v>
       </c>
       <c r="B2" t="n">
-        <v>95938</v>
+        <v>92429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632004</v>
+        <v>632308</v>
       </c>
       <c r="R2" t="n">
-        <v>6898915</v>
+        <v>6898776</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -743,19 +743,9 @@
           <t>2025-09-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128297500</v>
+        <v>128299233</v>
       </c>
       <c r="B3" t="n">
-        <v>92402</v>
+        <v>95965</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632308</v>
+        <v>632004</v>
       </c>
       <c r="R3" t="n">
-        <v>6898776</v>
+        <v>6898915</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -850,9 +840,19 @@
           <t>2025-09-08</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +882,7 @@
         <v>128297215</v>
       </c>
       <c r="B4" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128300242</v>
       </c>
       <c r="B5" t="n">
-        <v>98626</v>
+        <v>98653</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>128299710</v>
       </c>
       <c r="B6" t="n">
-        <v>95818</v>
+        <v>95845</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>128297225</v>
       </c>
       <c r="B7" t="n">
-        <v>80230</v>
+        <v>80257</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>128299667</v>
       </c>
       <c r="B8" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>128299487</v>
       </c>
       <c r="B9" t="n">
-        <v>92369</v>
+        <v>92396</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>128297461</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>128298782</v>
       </c>
       <c r="B11" t="n">
-        <v>91874</v>
+        <v>91901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41884-2025 artfynd.xlsx
+++ b/artfynd/A 41884-2025 artfynd.xlsx
@@ -879,45 +879,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128297215</v>
+        <v>128300242</v>
       </c>
       <c r="B4" t="n">
-        <v>80221</v>
+        <v>98653</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632389</v>
+        <v>632064</v>
       </c>
       <c r="R4" t="n">
-        <v>6898813</v>
+        <v>6898932</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -947,19 +956,9 @@
           <t>2025-09-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,54 +985,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128300242</v>
+        <v>128297215</v>
       </c>
       <c r="B5" t="n">
-        <v>98653</v>
+        <v>80221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632064</v>
+        <v>632389</v>
       </c>
       <c r="R5" t="n">
-        <v>6898932</v>
+        <v>6898813</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,9 +1053,19 @@
           <t>2025-09-08</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 41884-2025 artfynd.xlsx
+++ b/artfynd/A 41884-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128299233</v>
+        <v>128299710</v>
       </c>
       <c r="B2" t="n">
-        <v>95978</v>
+        <v>96338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632004</v>
+        <v>631959</v>
       </c>
       <c r="R2" t="n">
-        <v>6898915</v>
+        <v>6898908</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -743,19 +752,9 @@
           <t>2025-09-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128297500</v>
+        <v>128299233</v>
       </c>
       <c r="B3" t="n">
-        <v>92439</v>
+        <v>96458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +792,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632308</v>
+        <v>632004</v>
       </c>
       <c r="R3" t="n">
-        <v>6898776</v>
+        <v>6898915</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -850,9 +849,19 @@
           <t>2025-09-08</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,45 +888,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128297215</v>
+        <v>128299487</v>
       </c>
       <c r="B4" t="n">
-        <v>80225</v>
+        <v>92836</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>4740</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sotriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius lignyotus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632389</v>
+        <v>631994</v>
       </c>
       <c r="R4" t="n">
-        <v>6898813</v>
+        <v>6898910</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -947,19 +956,9 @@
           <t>2025-09-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128300242</v>
+        <v>128297500</v>
       </c>
       <c r="B5" t="n">
-        <v>98666</v>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,43 +996,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632064</v>
+        <v>632308</v>
       </c>
       <c r="R5" t="n">
-        <v>6898932</v>
+        <v>6898776</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1092,10 +1082,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128299710</v>
+        <v>128299667</v>
       </c>
       <c r="B6" t="n">
-        <v>95858</v>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,43 +1093,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631959</v>
+        <v>631960</v>
       </c>
       <c r="R6" t="n">
-        <v>6898908</v>
+        <v>6898907</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,10 +1179,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128297225</v>
+        <v>128300253</v>
       </c>
       <c r="B7" t="n">
-        <v>80261</v>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1209,21 +1190,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1214,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632389</v>
+        <v>632064</v>
       </c>
       <c r="R7" t="n">
-        <v>6898813</v>
+        <v>6898963</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1266,19 +1247,9 @@
           <t>2025-09-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,45 +1276,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128299667</v>
+        <v>128297461</v>
       </c>
       <c r="B8" t="n">
-        <v>92439</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>631960</v>
+        <v>632300</v>
       </c>
       <c r="R8" t="n">
-        <v>6898907</v>
+        <v>6898790</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1402,45 +1373,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128299487</v>
+        <v>128297215</v>
       </c>
       <c r="B9" t="n">
-        <v>92406</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4740</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sotriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius lignyotus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>631994</v>
+        <v>632389</v>
       </c>
       <c r="R9" t="n">
-        <v>6898910</v>
+        <v>6898813</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1470,9 +1441,19 @@
           <t>2025-09-08</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,32 +1480,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128297461</v>
+        <v>128297225</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>80468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1534,10 +1515,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632300</v>
+        <v>632389</v>
       </c>
       <c r="R10" t="n">
-        <v>6898790</v>
+        <v>6898813</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1567,9 +1548,19 @@
           <t>2025-09-08</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1596,43 +1587,60 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128298782</v>
+        <v>86783129</v>
       </c>
       <c r="B11" t="n">
-        <v>91911</v>
+        <v>57258</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6040186</v>
+        <v>100065</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+          <t>Furuskärsvägens vändplan med kalhyggen, Ännsiklandet, Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632013</v>
+        <v>632543</v>
       </c>
       <c r="R11" t="n">
-        <v>6898928</v>
+        <v>6898358</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1656,12 +1664,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2020-07-10</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2020-07-10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På långt håll.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1676,15 +1699,697 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>Rode Nordin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Rode Nordin, Bruno Nordin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>84835064</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Furuskärsvägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>632586</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6898727</v>
+      </c>
+      <c r="S12" t="n">
+        <v>16</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2020-04-26</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2020-04-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rode Nordin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bruno Nordin, Rode Nordin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>84836043</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Furuskärsvägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>632586</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6898727</v>
+      </c>
+      <c r="S13" t="n">
+        <v>16</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2020-04-26</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2020-04-26</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Rode Nordin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rode Nordin, Bruno Nordin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>84835001</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Furuskärsvägen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>632586</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6898727</v>
+      </c>
+      <c r="S14" t="n">
+        <v>16</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2020-04-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2020-04-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Rode Nordin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rode Nordin, Bruno Nordin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>72943882</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Furuskärsvägens vändplan med kalhyggen, Ännsiklandet, Njurunda, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>632543</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6898358</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2018-09-01</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2018-09-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Rode Nordin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Rode Nordin, Bruno Nordin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128300242</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ännsiksjön, Ännsiksjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>632064</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6898932</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128298782</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ännsiktjärnen, Ännsiktjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>632013</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6898928</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41884-2025 artfynd.xlsx
+++ b/artfynd/A 41884-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128299710</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128299233</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128299487</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128297500</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1176,6 +1201,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128299667</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1273,6 +1303,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300253</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1370,6 +1405,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128297461</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1477,6 +1517,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128297215</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1584,6 +1629,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128297225</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1708,6 +1758,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86783129</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1831,6 +1886,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84835064</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1949,6 +2009,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84836043</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2068,6 +2133,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84835001</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2187,6 +2257,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72943882</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2293,6 +2368,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300242</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2390,8 +2470,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128298782</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>